--- a/assets/constructions/examples/ctd_collet_round.xlsx
+++ b/assets/constructions/examples/ctd_collet_round.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,55 +534,81 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HF32-10</t>
+          <t>SC32-15.6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HYDRAULIC CHUCK COLLET COOLANT FLUSH TYPE</t>
+          <t>Переходные втулки SC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63.5</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>39</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HA-15.6</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>HA-10</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>HA-15.6</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DEREK</t>
+        </is>
+      </c>
       <c r="M2" t="n">
         <v>32</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>YG1_HC:32</t>
+          <t>DER_RC:HA-32</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -592,14 +618,20 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
-      </c>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DHC20-10</t>
+          <t>DHC32-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -613,7 +645,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50.5</v>
+        <v>60.5</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -622,12 +654,12 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -636,10 +668,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -649,7 +681,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>DER_RC:HA-20</t>
+          <t>DER_RC:HA-32</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -662,63 +694,71 @@
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>7176.81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HS32-12</t>
+          <t>32MHC180M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>63.5</v>
+        <v>64</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>39</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-18</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>32</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>YG1_RC:HA-32</t>
+          <t>WIDIA_MHC:HA-32</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -728,66 +768,62 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
-      </c>
+          <t>2010 / Tooling system Widia</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HS32-14</t>
+          <t>SC16-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YG1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>AMATI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>63.5</v>
+        <v>45</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>39</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>HA-14</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>HA-14</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>YG1</t>
-        </is>
-      </c>
+          <t>HA-11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>YG1_RC:HA-32</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -797,14 +833,20 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
-      </c>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K32-MT3</t>
+          <t>CK25-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -814,7 +856,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>END MILL COLLET (MT TYPE)</t>
+          <t>END MILL COLLET (CK TYPE)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -826,14 +868,16 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>MKG_L:3</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>32</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
@@ -842,7 +886,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>YG1_K:32</t>
+          <t>YG1_K:25</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -855,6 +899,12 @@
           <t>2021/YG1-TOOLING</t>
         </is>
       </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
